--- a/New_FacetMeanStress/Data_Files/SlideSlideTether/4NP_SlideSlide_Tether_CMS.xlsx
+++ b/New_FacetMeanStress/Data_Files/SlideSlideTether/4NP_SlideSlide_Tether_CMS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sjturner.FORTLEWIS\OneDrive - Fort Lewis College\Disc\FCMS results\SlideSlideTether\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brburrough\Repo_Git\Spinal-Disc-Replacement-Code\New_FacetMeanStress\Data_Files\SlideSlideTether\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="8_{A9C17385-2FE3-4A89-93B9-3256B4620A39}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{8B722470-6298-4C61-A095-B7EC2E75FEF9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55A1BA8-59F0-478F-B405-963801DA0264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2928" yWindow="2928" windowWidth="17280" windowHeight="9036" xr2:uid="{572B9DB9-15F5-4D56-9883-22A420EC1653}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{572B9DB9-15F5-4D56-9883-22A420EC1653}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="23">
   <si>
     <t>facet stress = facet contact force magnitude/facet contact area</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>4N Slide Slide Tether</t>
+  </si>
+  <si>
+    <t>5LL_6UL</t>
   </si>
 </sst>
 </file>
@@ -542,9 +545,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -582,7 +585,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -688,7 +691,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -830,7 +833,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -839,13 +842,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F6301C-52AE-49B8-AD87-FA2E3B1C4E48}">
   <dimension ref="A1:AN60"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="17" max="17" width="9.6640625" customWidth="1"/>
-    <col min="20" max="20" width="13.44140625" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -853,7 +856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -864,7 +867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -875,7 +878,7 @@
         <v>6</v>
       </c>
       <c r="P5" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="U5" t="s">
         <v>8</v>
@@ -890,7 +893,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1012,7 +1015,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
@@ -1150,7 +1153,7 @@
         <v>0.22002764139196385</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2.0512600000000001</v>
       </c>
@@ -1288,7 +1291,7 @@
         <v>0.21495919423161644</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2.1153300000000002</v>
       </c>
@@ -1426,7 +1429,7 @@
         <v>0.19797106863118372</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2.16533</v>
       </c>
@@ -1564,7 +1567,7 @@
         <v>0.18703853070686433</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2.2246999999999999</v>
       </c>
@@ -1702,7 +1705,7 @@
         <v>0.17552552122833878</v>
       </c>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2.2668900000000001</v>
       </c>
@@ -1840,7 +1843,7 @@
         <v>0.16805191009126566</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2.3262700000000001</v>
       </c>
@@ -1978,7 +1981,7 @@
         <v>0.15917905240222352</v>
       </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2.3684599999999998</v>
       </c>
@@ -2116,7 +2119,7 @@
         <v>0.15388953328924765</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2.4278300000000002</v>
       </c>
@@ -2254,7 +2257,7 @@
         <v>0.14740880630536707</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2.4542000000000002</v>
       </c>
@@ -2392,7 +2395,7 @@
         <v>0.14436983501850009</v>
       </c>
     </row>
-    <row r="17" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2.5061499999999999</v>
       </c>
@@ -2530,7 +2533,7 @@
         <v>0.13824200314004706</v>
       </c>
     </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2.5507599999999999</v>
       </c>
@@ -2668,7 +2671,7 @@
         <v>0.1325665281161913</v>
       </c>
     </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2.60453</v>
       </c>
@@ -2806,7 +2809,7 @@
         <v>0.12494485300711022</v>
       </c>
     </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2.65273</v>
       </c>
@@ -2944,7 +2947,7 @@
         <v>0.11772327360218338</v>
       </c>
     </row>
-    <row r="21" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2.7006199999999998</v>
       </c>
@@ -3082,7 +3085,7 @@
         <v>0.11149957099648648</v>
       </c>
     </row>
-    <row r="22" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2.75176</v>
       </c>
@@ -3220,7 +3223,7 @@
         <v>0.10513122282686936</v>
       </c>
     </row>
-    <row r="23" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2.80444</v>
       </c>
@@ -3358,7 +3361,7 @@
         <v>9.8390243433634769E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2.8583699999999999</v>
       </c>
@@ -3496,7 +3499,7 @@
         <v>9.1355999913363864E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2.9134199999999999</v>
       </c>
@@ -3634,7 +3637,7 @@
         <v>8.385727836239408E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2.9619599999999999</v>
       </c>
@@ -3772,7 +3775,7 @@
         <v>7.6622552355578716E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>3</v>
       </c>
@@ -3910,7 +3913,7 @@
         <v>7.0985721238676205E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>21</v>
       </c>
@@ -3918,7 +3921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -3929,12 +3932,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
       <c r="E32" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -3960,7 +3963,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>12</v>
       </c>
@@ -4082,7 +4085,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2</v>
       </c>
@@ -4220,7 +4223,7 @@
         <v>0.22002764139196385</v>
       </c>
     </row>
-    <row r="37" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2.0512600000000001</v>
       </c>
@@ -4358,7 +4361,7 @@
         <v>0.24649180438334933</v>
       </c>
     </row>
-    <row r="38" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2.1153300000000002</v>
       </c>
@@ -4496,7 +4499,7 @@
         <v>0.27651328213141557</v>
       </c>
     </row>
-    <row r="39" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2.1747100000000001</v>
       </c>
@@ -4634,7 +4637,7 @@
         <v>0.32483349744387235</v>
       </c>
     </row>
-    <row r="40" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2.20404</v>
       </c>
@@ -4772,7 +4775,7 @@
         <v>0.35293832063366448</v>
       </c>
     </row>
-    <row r="41" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2.2512099999999999</v>
       </c>
@@ -4910,7 +4913,7 @@
         <v>0.3979368133875722</v>
       </c>
     </row>
-    <row r="42" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2.3028900000000001</v>
       </c>
@@ -5048,7 +5051,7 @@
         <v>0.44467389202118157</v>
       </c>
     </row>
-    <row r="43" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2.3528600000000002</v>
       </c>
@@ -5186,7 +5189,7 @@
         <v>0.48911268205350339</v>
       </c>
     </row>
-    <row r="44" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2.4111699999999998</v>
       </c>
@@ -5324,7 +5327,7 @@
         <v>0.54102187948438352</v>
       </c>
     </row>
-    <row r="45" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2.4602499999999998</v>
       </c>
@@ -5462,7 +5465,7 @@
         <v>0.5901231519722272</v>
       </c>
     </row>
-    <row r="46" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2.51267</v>
       </c>
@@ -5600,7 +5603,7 @@
         <v>0.63630797278836604</v>
       </c>
     </row>
-    <row r="47" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2.5564</v>
       </c>
@@ -5738,7 +5741,7 @@
         <v>0.67669104973568628</v>
       </c>
     </row>
-    <row r="48" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2.6033400000000002</v>
       </c>
@@ -5876,7 +5879,7 @@
         <v>0.73436969829666865</v>
       </c>
     </row>
-    <row r="49" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2.6604800000000002</v>
       </c>
@@ -6014,7 +6017,7 @@
         <v>0.79233609048352716</v>
       </c>
     </row>
-    <row r="50" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2.7082199999999998</v>
       </c>
@@ -6152,7 +6155,7 @@
         <v>0.84172385325834576</v>
       </c>
     </row>
-    <row r="51" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2.7589999999999999</v>
       </c>
@@ -6290,7 +6293,7 @@
         <v>0.89554596120112107</v>
       </c>
     </row>
-    <row r="52" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2.8092299999999999</v>
       </c>
@@ -6428,7 +6431,7 @@
         <v>0.94818520226857839</v>
       </c>
     </row>
-    <row r="53" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2.8506100000000001</v>
       </c>
@@ -6566,7 +6569,7 @@
         <v>0.99257816063492887</v>
       </c>
     </row>
-    <row r="54" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2.90524</v>
       </c>
@@ -6704,7 +6707,7 @@
         <v>1.0521703880479913</v>
       </c>
     </row>
-    <row r="55" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2.9500299999999999</v>
       </c>
@@ -6842,7 +6845,7 @@
         <v>1.1017639201958629</v>
       </c>
     </row>
-    <row r="56" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>3</v>
       </c>
@@ -6980,7 +6983,7 @@
         <v>1.1587615865474035</v>
       </c>
     </row>
-    <row r="60" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:40" x14ac:dyDescent="0.25">
       <c r="E60" s="1"/>
       <c r="J60" s="1"/>
     </row>
@@ -7008,12 +7011,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7228,15 +7228,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D26554EB-CF90-446A-AC9D-C7406C1CA174}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F4F3A97-EEC4-4ED1-97E4-C94CA3B2F9C5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="f46330e8-2dd1-40f0-b204-735adb595018"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="fc18049f-9f74-4861-8203-09942736864f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7261,18 +7273,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F4F3A97-EEC4-4ED1-97E4-C94CA3B2F9C5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D26554EB-CF90-446A-AC9D-C7406C1CA174}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="f46330e8-2dd1-40f0-b204-735adb595018"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="fc18049f-9f74-4861-8203-09942736864f"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>